--- a/src/main/resources/excel/surver_eliminate_template.xlsx
+++ b/src/main/resources/excel/surver_eliminate_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\life\1\bootdo-main\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76206278-6F5E-403C-9A4D-29EC9283C106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F0ED3FC-F385-4C3E-8504-FBFE5499460E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -625,7 +625,14 @@
       <c r="R3" s="11"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F4"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -636,9 +643,19 @@
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="F5"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -649,8 +666,19 @@
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="5"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -661,8 +689,19 @@
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -673,6 +712,9 @@
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
     </row>
     <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
@@ -693,8 +735,12 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -712,11 +758,14 @@
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
       <c r="U9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -734,11 +783,14 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
       <c r="U10" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -756,11 +808,14 @@
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
       <c r="U11" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -778,11 +833,14 @@
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
       <c r="U12" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -800,11 +858,14 @@
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
       <c r="U13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -822,9 +883,12 @@
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -842,9 +906,12 @@
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -862,9 +929,19 @@
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="9:18" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -875,8 +952,19 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
-    </row>
-    <row r="18" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -887,8 +975,19 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-    </row>
-    <row r="19" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -899,8 +998,19 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-    </row>
-    <row r="20" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -911,8 +1021,19 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-    </row>
-    <row r="21" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -923,8 +1044,19 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
-    </row>
-    <row r="22" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -935,8 +1067,19 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-    </row>
-    <row r="23" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -947,8 +1090,19 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
-    </row>
-    <row r="24" spans="9:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -959,8 +1113,19 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-    </row>
-    <row r="25" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -971,8 +1136,19 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
-    </row>
-    <row r="26" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -983,8 +1159,19 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-    </row>
-    <row r="27" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -995,8 +1182,19 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
-    </row>
-    <row r="28" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1007,8 +1205,19 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-    </row>
-    <row r="29" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1019,8 +1228,11 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
-    </row>
-    <row r="30" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="I30" s="5"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
@@ -1032,7 +1244,7 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
     </row>
-    <row r="31" spans="9:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="I31" s="5"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1044,7 +1256,7 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
     </row>
-    <row r="32" spans="9:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="I32" s="5"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
